--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5306-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5306-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EF06319-F230-428F-B73A-CEDC3B530140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{669B6D96-4F3B-4453-ABF7-B1BAC959C844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{302E5F2D-DE0D-41DE-9A03-1A77D64BABD9}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1312A812-401C-402E-B324-802C54C0E5AB}"/>
   </bookViews>
   <sheets>
     <sheet name="5306-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1588,30 +1588,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17FEE5D-63C6-4D57-BE1A-23A20656CCB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33219C98-4556-47AF-A262-68FC8324FA7B}">
   <dimension ref="A1:X58"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1681,7 +1681,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1801,7 +1801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1909,7 +1909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>2024</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>29</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2023</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2022</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>29</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>29</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="49">
         <v>2021</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>2020</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2019</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>2018</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2017</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>2016</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>2015</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>2014</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
         <v>2013</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>2012</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="49">
         <v>2011</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>2010</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
         <v>2009</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>2008</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
         <v>2007</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>2006</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="49">
         <v>2005</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>2004</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="49">
         <v>2003</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="47">
         <v>2002</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="49">
         <v>2001</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="47">
         <v>2000</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="49">
         <v>1999</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="47">
         <v>1998</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="49">
         <v>1997</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="47">
         <v>1996</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="49">
         <v>1995</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="47">
         <v>1994</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="49">
         <v>1993</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="47">
         <v>1992</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="49" t="s">
         <v>69</v>
       </c>
